--- a/data/trans_orig/P16A_n_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas</t>
+          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,22 +716,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,34</t>
+          <t>1,16; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,91</t>
+          <t>1,67; 1,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 1,69</t>
+          <t>1,47; 1,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,4</t>
+          <t>2,02; 2,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,63</t>
+          <t>2,37; 2,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 2,42</t>
+          <t>2,16; 2,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 3,41</t>
+          <t>3,08; 3,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,07</t>
+          <t>1,9; 2,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 2,95</t>
+          <t>2,7; 2,95</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,1</t>
+          <t>0,65; 1,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,19</t>
+          <t>1,07; 1,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,27</t>
+          <t>1,34; 2,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,69</t>
+          <t>1,08; 1,7</t>
         </is>
       </c>
     </row>
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,64</t>
+          <t>0,45; 0,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,89</t>
+          <t>0,56; 0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,78</t>
+          <t>0,61; 0,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,09</t>
+          <t>0,89; 1,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,9</t>
+          <t>0,71; 0,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,12</t>
+          <t>0,87; 1,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,25</t>
+          <t>1,06; 1,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,97</t>
+          <t>0,74; 0,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,85</t>
+          <t>0,71; 0,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,75</t>
+          <t>0,68; 0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,08</t>
+          <t>0,97; 1,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 0,97</t>
+          <t>0,88; 0,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,27</t>
+          <t>0,9; 1,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,19</t>
+          <t>1,1; 1,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,68</t>
+          <t>1,56; 1,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,45</t>
+          <t>1,34; 1,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,27</t>
+          <t>1,71; 2,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,37</t>
+          <t>1,29; 1,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,2</t>
+          <t>1,13; 1,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,76</t>
+          <t>1,37; 1,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>3,21</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,75</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,35</t>
+          <t>1,16; 1,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,9</t>
+          <t>1,68; 1,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 1,71</t>
+          <t>1,47; 1,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,41</t>
+          <t>1,93; 2,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 1,82</t>
+          <t>1,65; 1,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 2,61</t>
+          <t>2,39; 2,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,41</t>
+          <t>2,18; 2,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 3,41</t>
+          <t>3,07; 3,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,58</t>
+          <t>1,46; 1,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,28</t>
+          <t>2,12; 2,29</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,08</t>
+          <t>1,9; 2,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 2,95</t>
+          <t>2,62; 2,86</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>1,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,79</t>
+          <t>0,69; 0,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,1</t>
+          <t>1,01; 1,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,19</t>
+          <t>1,07; 1,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,18</t>
+          <t>1,31; 1,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,7</t>
+          <t>1,18; 1,28</t>
         </is>
       </c>
     </row>
@@ -943,19 +943,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,8</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>0,98</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,87</t>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,08</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,63</t>
+          <t>0,46; 0,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,91</t>
+          <t>0,56; 0,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,11</t>
+          <t>0,87; 1,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 0,97</t>
+          <t>0,77; 0,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,26</t>
+          <t>1,09; 1,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,72</t>
+          <t>0,6; 0,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 0,94</t>
+          <t>0,74; 0,96</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,14</t>
+          <t>1,01; 1,15</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,07</t>
+          <t>0,96; 1,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,27 +1151,27 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,26</t>
+          <t>1,16; 1,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,19</t>
+          <t>1,1; 1,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,69</t>
+          <t>1,56; 1,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,46</t>
+          <t>1,34; 1,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,25</t>
+          <t>1,68; 1,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,36</t>
+          <t>1,28; 1,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,73</t>
+          <t>1,45; 1,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
+          <t>Población según el número de medicamentos consumidos por persona en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
